--- a/claves de acceso/Claves.xlsx
+++ b/claves de acceso/Claves.xlsx
@@ -36,18 +36,12 @@
     <t>jhonadmin</t>
   </si>
   <si>
-    <t>criss</t>
-  </si>
-  <si>
     <t>ana</t>
   </si>
   <si>
     <t>admin</t>
   </si>
   <si>
-    <t>empleado</t>
-  </si>
-  <si>
     <t>analista</t>
   </si>
   <si>
@@ -58,6 +52,12 @@
   </si>
   <si>
     <t>isaac123</t>
+  </si>
+  <si>
+    <t>carlos123</t>
+  </si>
+  <si>
+    <t>emilio123</t>
   </si>
 </sst>
 </file>
@@ -442,7 +442,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2">
         <v>123</v>
@@ -453,7 +453,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>123</v>
@@ -464,7 +464,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
         <v>123456</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
         <v>123456</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>123456</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>123456</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>123456</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>1234</v>
